--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF9A632-3E11-4EC3-B29D-06AA7648921D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05420438-C935-449B-8EBF-51E2A1C3AB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18000" yWindow="-13440" windowWidth="9675" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -143,6 +143,9 @@
       <t>モノ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バッグ</t>
   </si>
 </sst>
 </file>
@@ -500,8 +503,9 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -663,10 +667,10 @@
       </c>
       <c r="D8" s="3">
         <f>VLOOKUP(E8,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F8" s="3">
         <v>-1</v>
@@ -683,10 +687,10 @@
       </c>
       <c r="D9" s="3">
         <f>VLOOKUP(E9,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" s="3">
         <v>-1</v>
@@ -703,10 +707,10 @@
       </c>
       <c r="D10" s="3">
         <f>VLOOKUP(E10,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F10" s="3">
         <v>-1</v>
@@ -723,10 +727,10 @@
       </c>
       <c r="D11" s="3">
         <f>VLOOKUP(E11,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F11" s="3">
         <v>-1</v>

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05420438-C935-449B-8EBF-51E2A1C3AB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5062CC9F-E4D2-40CD-A5E2-CFB6163EFDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18000" yWindow="-13440" windowWidth="9675" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15195" yWindow="-13635" windowWidth="9675" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -547,7 +547,7 @@
         <v>5</v>
       </c>
       <c r="F2" s="3">
-        <v>-1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -569,7 +569,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="3">
-        <v>-1</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -591,7 +591,7 @@
         <v>6</v>
       </c>
       <c r="F4" s="3">
-        <v>-1</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -613,7 +613,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="3">
-        <v>-1</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6">

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5062CC9F-E4D2-40CD-A5E2-CFB6163EFDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A248A92-4404-4D3D-B1C5-F64E01250408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15195" yWindow="-13635" windowWidth="9675" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -146,6 +146,53 @@
   </si>
   <si>
     <t>バッグ</t>
+  </si>
+  <si>
+    <t>焼けた食べ物</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腐った食べ物</t>
+    <rPh sb="0" eb="1">
+      <t>クサ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>burnID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>lotID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒こげの食べ物</t>
+    <rPh sb="0" eb="1">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -188,7 +235,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -211,15 +258,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -500,15 +559,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -527,8 +589,14 @@
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="3">
         <v>0</v>
       </c>
@@ -549,8 +617,14 @@
       <c r="F2" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -571,8 +645,14 @@
       <c r="F3" s="3">
         <v>101</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="3">
         <v>100</v>
       </c>
@@ -580,7 +660,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="3">
-        <f t="shared" ref="C4:C11" si="0">A4+12000</f>
+        <f t="shared" ref="C4:C14" si="0">A4+12000</f>
         <v>12100</v>
       </c>
       <c r="D4" s="3">
@@ -593,8 +673,14 @@
       <c r="F4" s="3">
         <v>102</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="3">
+        <v>102</v>
+      </c>
+      <c r="H4" s="3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="3">
         <v>101</v>
       </c>
@@ -615,124 +701,250 @@
       <c r="F5" s="3">
         <v>103</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="3">
+        <v>102</v>
+      </c>
+      <c r="H5" s="3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="3">
-        <v>200</v>
-      </c>
-      <c r="B6" s="3"/>
+        <v>102</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="C6" s="3">
-        <f t="shared" si="0"/>
-        <v>12200</v>
+        <f t="shared" ref="C6:C7" si="1">A6+12000</f>
+        <v>12102</v>
       </c>
       <c r="D6" s="3">
         <f>VLOOKUP(E6,reference!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="3">
+        <v>104</v>
+      </c>
+      <c r="H6" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3">
-        <v>300</v>
-      </c>
-      <c r="B7" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="C7" s="3">
-        <f t="shared" si="0"/>
-        <v>12300</v>
+        <f t="shared" si="1"/>
+        <v>12103</v>
       </c>
       <c r="D7" s="3">
         <f>VLOOKUP(E7,reference!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" s="3">
+        <v>102</v>
+      </c>
+      <c r="H7" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="3">
-        <v>400</v>
-      </c>
-      <c r="B8" s="3"/>
+        <v>104</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="C8" s="3">
-        <f t="shared" si="0"/>
-        <v>12400</v>
+        <f t="shared" ref="C8" si="2">A8+12000</f>
+        <v>12104</v>
       </c>
       <c r="D8" s="3">
         <f>VLOOKUP(E8,reference!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F8" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3">
         <f t="shared" si="0"/>
-        <v>12500</v>
+        <v>12200</v>
       </c>
       <c r="D9" s="3">
         <f>VLOOKUP(E9,reference!A:B,2,FALSE)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3">
         <f t="shared" si="0"/>
-        <v>12600</v>
+        <v>12300</v>
       </c>
       <c r="D10" s="3">
         <f>VLOOKUP(E10,reference!A:B,2,FALSE)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F10" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3">
         <f t="shared" si="0"/>
-        <v>12700</v>
+        <v>12400</v>
       </c>
       <c r="D11" s="3">
         <f>VLOOKUP(E11,reference!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G11" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="3">
+        <v>500</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3">
+        <f t="shared" si="0"/>
+        <v>12500</v>
+      </c>
+      <c r="D12" s="3">
+        <f>VLOOKUP(E12,reference!A:B,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="3">
+        <v>600</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3">
+        <f t="shared" si="0"/>
+        <v>12600</v>
+      </c>
+      <c r="D13" s="3">
+        <f>VLOOKUP(E13,reference!A:B,2,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="3">
+        <v>700</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3">
+        <f t="shared" si="0"/>
+        <v>12700</v>
+      </c>
+      <c r="D14" s="3">
+        <f>VLOOKUP(E14,reference!A:B,2,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F14" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="3">
         <v>-1</v>
       </c>
     </row>
@@ -747,7 +959,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E11</xm:sqref>
+          <xm:sqref>E2:E14</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A248A92-4404-4D3D-B1C5-F64E01250408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69698901-0B32-4C87-A1E8-AE0370BE6AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="28">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -191,6 +191,28 @@
     </rPh>
     <rPh sb="6" eb="7">
       <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MinValue</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MaxValue</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杖１</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杖２</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -559,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
@@ -568,9 +590,11 @@
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -595,8 +619,14 @@
       <c r="H1" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="3">
         <v>0</v>
       </c>
@@ -623,8 +653,14 @@
       <c r="H2" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J2" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -651,8 +687,14 @@
       <c r="H3" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J3" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="3">
         <v>100</v>
       </c>
@@ -660,7 +702,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="3">
-        <f t="shared" ref="C4:C14" si="0">A4+12000</f>
+        <f t="shared" ref="C4:C15" si="0">A4+12000</f>
         <v>12100</v>
       </c>
       <c r="D4" s="3">
@@ -679,8 +721,14 @@
       <c r="H4" s="3">
         <v>103</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="3">
         <v>101</v>
       </c>
@@ -707,8 +755,14 @@
       <c r="H5" s="3">
         <v>103</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J5" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="3">
         <v>102</v>
       </c>
@@ -735,8 +789,14 @@
       <c r="H6" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J6" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="3">
         <v>103</v>
       </c>
@@ -763,8 +823,14 @@
       <c r="H7" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="3">
         <v>104</v>
       </c>
@@ -791,12 +857,20 @@
       <c r="H8" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J8" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="3">
         <v>200</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="C9" s="3">
         <f t="shared" si="0"/>
         <v>12200</v>
@@ -809,7 +883,7 @@
         <v>7</v>
       </c>
       <c r="F9" s="3">
-        <v>-1</v>
+        <v>104</v>
       </c>
       <c r="G9" s="3">
         <v>-1</v>
@@ -817,48 +891,62 @@
       <c r="H9" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3">
+        <v>4</v>
+      </c>
+      <c r="J9" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="3">
-        <v>300</v>
-      </c>
-      <c r="B10" s="3"/>
+        <v>201</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="C10" s="3">
-        <f t="shared" si="0"/>
-        <v>12300</v>
+        <f t="shared" ref="C10" si="3">A10+12000</f>
+        <v>12201</v>
       </c>
       <c r="D10" s="3">
         <f>VLOOKUP(E10,reference!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="3">
+        <v>104</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
         <v>3</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G10" s="3">
-        <v>-1</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3">
         <f t="shared" si="0"/>
-        <v>12400</v>
+        <v>12300</v>
       </c>
       <c r="D11" s="3">
         <f>VLOOKUP(E11,reference!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F11" s="3">
         <v>-1</v>
@@ -869,22 +957,28 @@
       <c r="H11" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3">
         <f t="shared" si="0"/>
-        <v>12500</v>
+        <v>12400</v>
       </c>
       <c r="D12" s="3">
         <f>VLOOKUP(E12,reference!A:B,2,FALSE)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F12" s="3">
         <v>-1</v>
@@ -895,22 +989,28 @@
       <c r="H12" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J12" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3">
         <f t="shared" si="0"/>
-        <v>12600</v>
+        <v>12500</v>
       </c>
       <c r="D13" s="3">
         <f>VLOOKUP(E13,reference!A:B,2,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3">
         <v>-1</v>
@@ -921,30 +1021,74 @@
       <c r="H13" s="3">
         <v>-1</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J13" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3">
         <f t="shared" si="0"/>
-        <v>12700</v>
+        <v>12600</v>
       </c>
       <c r="D14" s="3">
         <f>VLOOKUP(E14,reference!A:B,2,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="3">
+        <v>700</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3">
+        <f t="shared" si="0"/>
+        <v>12700</v>
+      </c>
+      <c r="D15" s="3">
+        <f>VLOOKUP(E15,reference!A:B,2,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="F15" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G15" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I15" s="3">
+        <v>-1</v>
+      </c>
+      <c r="J15" s="3">
         <v>-1</v>
       </c>
     </row>
@@ -959,7 +1103,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E14</xm:sqref>
+          <xm:sqref>E2:E15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
